--- a/data/trans_orig/IP06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55568</t>
+          <t>55446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45238</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>60016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>90225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111501</t>
+          <t>111879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55752</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>49655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73567</t>
+          <t>72238</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101311</t>
+          <t>99477</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>82320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110405</t>
+          <t>110095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101667</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131677</t>
+          <t>130978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191674</t>
+          <t>192947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234331</t>
+          <t>233288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252121</t>
+          <t>252566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>281711</t>
+          <t>284199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290398</t>
+          <t>292504</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>326057</t>
+          <t>326684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>554723</t>
+          <t>551509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>598543</t>
+          <t>596822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71359</t>
+          <t>70007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92049</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139719</t>
+          <t>139321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168961</t>
+          <t>169824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73926</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95436</t>
+          <t>96633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>62661</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82459</t>
+          <t>82797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142772</t>
+          <t>142696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172511</t>
+          <t>173428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>91919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>54079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78662</t>
+          <t>78862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>125830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>161341</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>174733</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>214808</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184964</t>
+          <t>185100</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>224050</t>
+          <t>223547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>371162</t>
+          <t>371967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>426653</t>
+          <t>425913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>378413</t>
+          <t>376609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>419881</t>
+          <t>419789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>414479</t>
+          <t>415883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>455645</t>
+          <t>457012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>805963</t>
+          <t>806318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>865294</t>
+          <t>866615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72064</t>
+          <t>72013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63079</t>
+          <t>63261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110429</t>
+          <t>110907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130895</t>
+          <t>130779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>48695</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51839</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62762</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>91678</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99147</t>
+          <t>100789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129564</t>
+          <t>130960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122130</t>
+          <t>122618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154314</t>
+          <t>156368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232763</t>
+          <t>231858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275125</t>
+          <t>276740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277244</t>
+          <t>276421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310533</t>
+          <t>308821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>286893</t>
+          <t>286285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322229</t>
+          <t>322300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>572283</t>
+          <t>574068</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619718</t>
+          <t>622002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64089</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85455</t>
+          <t>84907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78730</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148499</t>
+          <t>148923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179550</t>
+          <t>178369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74098</t>
+          <t>73988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96026</t>
+          <t>95153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>85228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143421</t>
+          <t>144952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174241</t>
+          <t>174775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50192</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76629</t>
+          <t>76582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>99474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133466</t>
+          <t>134214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>178892</t>
+          <t>179692</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>218660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>221128</t>
+          <t>220417</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>262133</t>
+          <t>263636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>412212</t>
+          <t>409905</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>467745</t>
+          <t>468940</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>423095</t>
+          <t>422645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>465248</t>
+          <t>464125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>412079</t>
+          <t>409920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>457420</t>
+          <t>456144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>845576</t>
+          <t>846747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>906414</t>
+          <t>907949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80649</t>
+          <t>81432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97095</t>
+          <t>97733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34679</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>55378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69472</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99019</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13804</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71811</t>
+          <t>72798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99424</t>
+          <t>98548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78928</t>
+          <t>78841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106424</t>
+          <t>105919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157653</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196503</t>
+          <t>196541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315020</t>
+          <t>317978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>348168</t>
+          <t>349700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329162</t>
+          <t>330018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359981</t>
+          <t>361743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>657181</t>
+          <t>655089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>703726</t>
+          <t>700425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>62266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60122</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81537</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128841</t>
+          <t>129259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159754</t>
+          <t>159629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81110</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102215</t>
+          <t>102804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97761</t>
+          <t>97072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>120109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183856</t>
+          <t>186374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215674</t>
+          <t>216612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67429</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>76897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>145741</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>181036</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149857</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>187645</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>357538</t>
+          <t>356708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447027</t>
+          <t>444353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>487702</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>479772</t>
+          <t>483533</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>524566</t>
+          <t>524644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>939566</t>
+          <t>940932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>999045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15983</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10714</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26477</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33866</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33466</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11341</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22489</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52079</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -835,92 +835,92 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6298</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15294</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21629</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,91%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16945</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11629</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23174</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11716</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23368</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15294</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10332</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22103</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53547</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45937</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60958</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47445</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39966</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55446</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>40249</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>55304</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>52,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>61,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>53547</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>45809</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>60016</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90225</t>
+          <t>90154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111879</t>
+          <t>111781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -1174,57 +1174,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1291,74 +1291,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39672</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>31325</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50310</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45324</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35698</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>55967</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>35313</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>10,94%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>39672</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>30379</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49655</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>129</t>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>71993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>100281</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11030</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17204</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6012</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11188</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11030</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6529</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1517,107 +1517,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>116037</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102321</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131637</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>95416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82320</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110095</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82776</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109348</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>116037</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>101669</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130978</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>211453</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>190028</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>232375</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>21,34%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>211453</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>192947</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>233288</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>309587</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>290563</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>324289</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>61,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>402</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>267378</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>252566</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>284199</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>252790</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>282932</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>64,56%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>309587</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>292504</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>326684</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>64,99%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>551509</t>
+          <t>553471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>596822</t>
+          <t>599400</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -1743,57 +1743,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>476326</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>476326</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>476326</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>414131</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>414131</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>414131</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>476326</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>476326</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>476326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5641</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15419</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5975</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11100</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11241</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9930</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5652</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16783</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1978,67 +1978,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>2141</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>448</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>4762</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2141</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73463</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63540</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84084</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>81272</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>70007</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91641</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>70586</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>91771</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>73463</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>63538</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>83248</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139321</t>
+          <t>139832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169824</t>
+          <t>170702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72604</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62967</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>82774</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>85095</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>75004</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96633</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>74435</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>95486</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72604</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>62661</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>82797</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142696</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173428</t>
+          <t>172577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -2312,57 +2312,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2429,72 +2429,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>65586</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>55302</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>79809</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>77777</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>64989</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>91919</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>64877</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>93141</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,45%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>65586</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>54079</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>78862</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>127095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164639</t>
+          <t>162594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2542,72 +2542,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9597</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22650</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7736</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13261</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>13622</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>9314</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>21953</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2655,72 +2655,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>204794</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>187188</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>225296</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>31,23%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>193634</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>175235</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>214808</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>175364</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>212426</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,81%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>204794</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>185100</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>223547</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>371967</t>
+          <t>368864</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>425913</t>
+          <t>425587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>435737</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>414038</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>455629</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,41%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>63,17%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>595</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>399919</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>376609</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>419789</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>379624</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>420270</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>58,89%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>55,46%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>435737</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>415883</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>457012</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>806318</t>
+          <t>805429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>866615</t>
+          <t>867110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -2881,57 +2881,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>721308</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>721308</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>721308</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>679065</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>679065</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>679065</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>721308</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>721308</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>721308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3061,7 +3061,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3229,72 +3229,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17285</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11699</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24410</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12878</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7827</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19066</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,18%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17285</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11501</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24436</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22596</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>39411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3342,72 +3342,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2427</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -3455,72 +3455,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12182</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18319</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10115</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15986</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5720</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15546</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12182</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7387</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19107</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3568,72 +3568,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56097</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48901</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63057</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>65413</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58241</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>72013</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>57729</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>71553</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>56097</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>47794</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63261</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110907</t>
+          <t>110983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -3681,57 +3681,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90833</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>90833</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>90833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3798,72 +3798,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39484</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30814</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>51067</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>38078</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>29433</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48695</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>28736</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>49225</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>39484</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>29246</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50729</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>63531</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91678</t>
+          <t>94012</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3911,74 +3911,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11843</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6955</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18455</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5714</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2685</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10749</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2766</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10858</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11843</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6747</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18619</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4024,72 +4024,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139320</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121710</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154269</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>114669</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100789</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130960</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100142</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130516</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>25,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139320</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122618</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156368</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231858</t>
+          <t>232921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276740</t>
+          <t>276943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -4137,72 +4137,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>303799</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>287017</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>322177</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>61,44%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>65,16%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>422</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>293118</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>276421</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>308821</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>276262</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>309975</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>64,91%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>68,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>303799</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>286285</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>322300</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>61,44%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>574068</t>
+          <t>572465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622002</t>
+          <t>618976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -4250,57 +4250,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>451579</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>451579</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>451579</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4367,72 +4367,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2329</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10429</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3169</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7816</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8307</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5556</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10648</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4480,64 +4480,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>3834</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>8517</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8262</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>3471</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>7534</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4593,72 +4593,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89320</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77727</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>99517</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,86%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>74552</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>64362</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>84907</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>63804</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>84801</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>89320</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>77889</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>100489</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148923</t>
+          <t>146978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178369</t>
+          <t>178593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -4706,72 +4706,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73881</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>63930</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>85726</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>49,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>85258</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73988</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>95153</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>75218</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>96462</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>51,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>73881</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>63321</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>85228</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>144148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174775</t>
+          <t>175881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -4819,57 +4819,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4936,72 +4936,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>62325</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>49390</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>74849</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>54125</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>44080</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>68015</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>42874</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>62325</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>50070</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>76582</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99474</t>
+          <t>99426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134214</t>
+          <t>136116</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5049,72 +5049,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15943</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10359</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>23653</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>11975</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7528</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19222</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7168</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>15943</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>10899</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>23730</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5162,72 +5162,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>240821</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>219311</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>261898</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>34,79%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>199335</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>179692</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>218660</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>181317</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>220259</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,11%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>240821</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>220417</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>263636</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>409905</t>
+          <t>413250</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>468940</t>
+          <t>469319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -5275,72 +5275,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>433777</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>411341</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>457159</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>57,62%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>54,64%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>443788</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>422645</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>464125</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>421270</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>464794</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>62,57%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59,59%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>65,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>433777</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>409920</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>456144</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>57,62%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>846747</t>
+          <t>844891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>907949</t>
+          <t>907408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -5388,57 +5388,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>709224</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>709224</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>709224</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5568,7 +5568,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5736,72 +5736,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14542</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9845</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21711</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11609</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7272</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17731</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6993</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17041</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14542</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9488</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21131</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34154</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -5849,107 +5849,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4355</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4238</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5962,72 +5962,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9300</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4261</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8861</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8966</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8876</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -6075,72 +6075,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48238</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41426</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53871</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>41749</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35764</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46826</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35742</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46928</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48238</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>41482</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53786</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81432</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97733</t>
+          <t>98708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -6188,57 +6188,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57619</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>57619</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>57619</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6305,72 +6305,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34434</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56176</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>38377</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28474</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48608</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>28904</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>49921</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>8,15%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34843</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>55378</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68990</t>
+          <t>68637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98867</t>
+          <t>97202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -6418,72 +6418,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3467</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12212</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13843</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8123</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8598</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21244</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6620</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2956</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>29168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -6531,72 +6531,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91586</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106033</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>85095</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72798</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98548</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71383</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97657</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>18,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>91586</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>78841</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105919</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>156163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196541</t>
+          <t>197666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -6644,72 +6644,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>345879</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>328625</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>362851</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>333569</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>317978</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>349700</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>317556</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>348829</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>70,84%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>345879</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>330018</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>361743</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>655089</t>
+          <t>657438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>700425</t>
+          <t>701050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,11%</t>
         </is>
       </c>
     </row>
@@ -6757,57 +6757,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>488048</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>488048</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>488048</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>470884</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>470884</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>470884</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>488048</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>488048</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>488048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6874,72 +6874,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5232</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2371</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10245</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10144</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4190</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6987,72 +6987,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6768</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2703</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7100,72 +7100,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70865</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>60258</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81580</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72786</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>62266</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>83945</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62917</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>83981</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,32%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>70865</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>60386</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82367</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129259</t>
+          <t>127750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159629</t>
+          <t>157896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -7213,72 +7213,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109737</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98361</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120690</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>91904</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>81365</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102804</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80159</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>101994</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>53,44%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>47,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>109737</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>97072</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>120109</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186374</t>
+          <t>187019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216612</t>
+          <t>217665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -7326,57 +7326,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>171987</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>171987</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>171987</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7443,72 +7443,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>62695</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>50613</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>77061</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>55218</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>45443</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>69407</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>44721</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>67633</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>62695</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>50467</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>76897</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102634</t>
+          <t>102160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135872</t>
+          <t>136695</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -7556,72 +7556,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10569</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6273</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16985</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>15908</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10658</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24300</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9964</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>22721</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10569</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6155</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>17172</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7669,72 +7669,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>167038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>148193</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>186121</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>162141</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>145741</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>181763</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>144810</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>180056</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>23,15%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>167038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>149442</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>185994</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>304775</t>
+          <t>302408</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>356708</t>
+          <t>355449</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -7782,72 +7782,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>503855</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>482431</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>524772</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>67,71%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>704</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>467223</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>444353</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>485727</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>447627</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>488786</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>66,7%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>63,43%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>69,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>503855</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>483533</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>524644</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>67,71%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>940932</t>
+          <t>939830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>999045</t>
+          <t>997735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -7895,57 +7895,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>744157</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>744157</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>744157</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1056</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>700491</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>700491</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>700491</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>744157</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>744157</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>744157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
